--- a/stories/arbres/ATOM-JEU.REG.002-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Henri est dans le salon avec papa. Des cubes sont au sol. Papa dit une règle. La règle : on attend. Puis on pose un cube. Henri tend la main. Papa va rappeler la règle une fois. Il dit : on attend. C'est une règle. Henri attend. Puis il pose un cube. Papa dit : tu as suivi la règle. Plus tard, au jardin, papa dit une règle. La règle : on passe le ballon. Puis on s'arrête. Henri veut le ballon. Papa va rappeler la règle une fois. Il dit : on passe, puis on s'arrête. Henri passe le ballon. Il s'arrête. Même leçon, autre jeu. Une règle. La rappeler. Henri la suit.</t>
+          <t>Henri est dans le salon avec papa. Des cubes sont au sol. Papa dit une règle. La règle : on attend. Puis on pose un cube. Henri tend la main. Papa va rappeler la règle une fois. On attend. C'est une règle. Henri attend. Puis il pose un cube. Tu as suivi la règle. Plus tard, au jardin, papa dit une règle. La règle : on passe le ballon. Puis on s'arrête. Henri veut le ballon. Papa va rappeler la règle une fois. On passe, puis on s'arrête. Henri passe le ballon. Il s'arrête. Même leçon, autre jeu. Une règle. La rappeler. Henri la suit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Henri est dans le salon avec papa. Des cubes sont au sol. Papa dit une règle. La règle : on attend. Puis on pose un cube. Henri tend la main. Papa va rappeler la règle une fois.
+narrateur|On attend. C'est une règle.
+narrateur|Henri attend. Puis il pose un cube.
+papa|Tu as suivi la règle. Plus tard, au jardin, papa dit une règle.
+narrateur|La règle : on passe le ballon. Puis on s'arrête. Henri veut le ballon. Papa va rappeler la règle une fois.
+narrateur|On passe, puis on s'arrête.
+narrateur|Henri passe le ballon. Il s'arrête. Même leçon, autre jeu. Une règle. La rappeler. Henri la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Henri joue. Que suit-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Henri a suivi une règle. Papa l'a rappelée. Cubes, puis ballon.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le ballon. Henri donne la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Henri passe le ballon. Il s'arrête. Même leçon, autre jeu. Une règle. La rappeler. Henri la suit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Henri joue. Que suit-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Henri a suivi une règle. Papa l'a rappelée. Cubes, puis ballon.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Papa range le ballon. Henri donne la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.002-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Henri suit une règle, deux jeux</t>
+          <t>Les cubes de Nino, puis le jardin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino suit une règle aux cubes, puis au ballon dans l'herbe. Papa rappelle une fois, chaque fois.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Henri est dans le salon avec papa. Des cubes sont au sol. Papa dit une règle. La règle : on attend. Puis on pose un cube. Henri tend la main. Papa va rappeler la règle une fois. On attend. C'est une règle. Henri attend. Puis il pose un cube. Tu as suivi la règle. Plus tard, au jardin, papa dit une règle. La règle : on passe le ballon. Puis on s'arrête. Henri veut le ballon. Papa va rappeler la règle une fois. On passe, puis on s'arrête. Henri passe le ballon. Il s'arrête. Même leçon, autre jeu. Une règle. La rappeler. Henri la suit.</t>
+          <t>Une miette de toast reste sur la nappe. Le soleil du matin entre par la fenêtre. Il fait un carré chaud sur le parquet. Une caisse de cubes attend près du tapis. Un cube orange a roulé sous la chaise. L'odeur du toast est encore là. La nappe a un pli, tout près de la miette. Le bois de la caisse est lisse. Une mouche se pose sur la nappe. Elle s'en va. La miette reste. Le parquet est tiède sous le carré. Tu as vu le carré de soleil, Nino ? Oui, papa. Il est chaud. En ce moment, papa pose un cube au sol. Les cubes sentent le bois sec. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Nino attend, un cube orange dans la main. Puis il pose le cube. Le bois fait clic sur le parquet. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Nino. Une règle. On attend. Puis on pose. Oui. On la rappelle. Tu la suis. Plus tard, au jardin, l'air sent l'herbe. Un ballon souple attend près du bac. L'herbe est un peu mouillée sous les pieds. Une règle. On passe le ballon. Puis on s'arrête. On attend. Je me souviens. Comme les cubes. Oui. Je te la rappelle une fois. Nino attend. Puis il passe le ballon. Il s'arrête. L'herbe colle un peu. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. Cubes, puis ballon. Oui. On la rappelle. On la suit. Tu as fait du bon travail. Le bac reste près de l'herbe. Tu as attendu aux cubes, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Nino. Nino essuie ses mains dans l'herbe. Tu as attendu, chaque fois ? Oui. Cubes, puis ballon. Une règle. Je la rappelle. Tu la suis. Le bac sent un peu le plastique chaud. Une goutte d'herbe reste sur le ballon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Henri est dans le salon avec papa. Des cubes sont au sol. Papa dit une règle. La règle : on attend. Puis on pose un cube. Henri tend la main. Papa va rappeler la règle une fois.
-narrateur|On attend. C'est une règle.
-narrateur|Henri attend. Puis il pose un cube.
-papa|Tu as suivi la règle. Plus tard, au jardin, papa dit une règle.
-narrateur|La règle : on passe le ballon. Puis on s'arrête. Henri veut le ballon. Papa va rappeler la règle une fois.
-narrateur|On passe, puis on s'arrête.
-narrateur|Henri passe le ballon. Il s'arrête. Même leçon, autre jeu. Une règle. La rappeler. Henri la suit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une miette de toast reste sur la nappe.
+narrateur|Le soleil du matin entre par la fenêtre.
+narrateur|Il fait un carré chaud sur le parquet.
+narrateur|Une caisse de cubes attend près du tapis.
+narrateur|Un cube orange a roulé sous la chaise.
+narrateur|L'odeur du toast est encore là.
+narrateur|La nappe a un pli, tout près de la miette.
+narrateur|Le bois de la caisse est lisse.
+narrateur|Une mouche se pose sur la nappe.
+narrateur|Elle s'en va.
+narrateur|La miette reste.
+narrateur|Le parquet est tiède sous le carré.
+papa|Tu as vu le carré de soleil, Nino ?
+enfant-m|Oui, papa. Il est chaud.
+narrateur|En ce moment, papa pose un cube au sol.
+narrateur|Les cubes sentent le bois sec.
+papa|Une règle. On attend.
+papa|Puis on pose un cube.
+enfant-m|J'ai envie de poser.
+papa|On attend. Je te la rappelle une fois.
+papa|C'est la règle.
+narrateur|Nino attend, un cube orange dans la main.
+narrateur|Puis il pose le cube.
+narrateur|Le bois fait clic sur le parquet.
+enfant-m|Clic.
+papa|Tu as suivi la règle.
+papa|Tu as attendu. Bravo, Nino.
+enfant-m|Une règle. On attend. Puis on pose.
+papa|Oui. On la rappelle. Tu la suis.
+narrateur|Plus tard, au jardin, l'air sent l'herbe.
+narrateur|Un ballon souple attend près du bac.
+narrateur|L'herbe est un peu mouillée sous les pieds.
+papa|Une règle. On passe le ballon.
+papa|Puis on s'arrête. On attend.
+enfant-m|Je me souviens. Comme les cubes.
+papa|Oui. Je te la rappelle une fois.
+narrateur|Nino attend.
+narrateur|Puis il passe le ballon.
+narrateur|Il s'arrête.
+narrateur|L'herbe colle un peu.
+papa|Tu as suivi la règle dite.
+papa|Au ballon, la même règle. Bravo.
+enfant-m|Une règle. Cubes, puis ballon.
+papa|Oui. On la rappelle. On la suit.
+papa|Tu as fait du bon travail.
+narrateur|Le bac reste près de l'herbe.
+papa|Tu as attendu aux cubes, puis au ballon ?
+enfant-m|Oui. Deux jeux. Une règle.
+papa|Bravo, Nino.
+narrateur|Nino essuie ses mains dans l'herbe.
+papa|Tu as attendu, chaque fois ?
+enfant-m|Oui. Cubes, puis ballon.
+papa|Une règle. Je la rappelle. Tu la suis.
+narrateur|Le bac sent un peu le plastique chaud.
+narrateur|Une goutte d'herbe reste sur le ballon.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1405,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Henri joue. Que suit-il ?</t>
+          <t>Nino joue. Que suit-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,10 +1561,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Henri joue. Que suit-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino joue.
+narrateur|Que suit-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Henri a suivi une règle. Papa l'a rappelée. Cubes, puis ballon.</t>
+          <t>Nino a suivi une règle. Papa l'a rappelée. Cubes, puis ballon. Deux jeux. Tu as suivi la règle ? Oui, papa. On attend. Bravo. On la rappelle, et on la suit. Le ballon repose près du bac.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,10 +1733,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Henri a suivi une règle. Papa l'a rappelée. Cubes, puis ballon.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino a suivi une règle.
+narrateur|Papa l'a rappelée. Cubes, puis ballon.
+papa|Deux jeux. Tu as suivi la règle ?
+enfant-m|Oui, papa. On attend.
+papa|Bravo. On la rappelle, et on la suit.
+narrateur|Le ballon repose près du bac.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,7 +1765,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Henri donne la main.</t>
+          <t>On range le ballon ? Oui, papa. Papa range le ballon dans le bac. Nino donne la main. On rentre. Le toast est fini. Oui. L'herbe est mouillée. Le carré de soleil a bougé. On range aussi les cubes, plus tard ? Oui. Dans la caisse. L'odeur du toast n'est plus là.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,10 +1905,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le ballon. Henri donne la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>papa|On range le ballon ?
+enfant-m|Oui, papa.
+narrateur|Papa range le ballon dans le bac.
+narrateur|Nino donne la main.
+papa|On rentre. Le toast est fini.
+enfant-m|Oui. L'herbe est mouillée.
+narrateur|Le carré de soleil a bougé.
+papa|On range aussi les cubes, plus tard ?
+enfant-m|Oui. Dans la caisse.
+narrateur|L'odeur du toast n'est plus là.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,7 +1941,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les chaussures de Nino sont un peu humides. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Nino. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,10 +2081,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Les chaussures de Nino sont un peu humides.
+enfant-m|J'ai attendu. Deux fois.
+papa|Oui. Tu as suivi la règle.
+papa|Bravo, Nino.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une miette de toast reste sur la nappe. Le soleil du matin entre par la fenêtre. Il fait un carré chaud sur le parquet. Une caisse de cubes attend près du tapis. Un cube orange a roulé sous la chaise. L'odeur du toast est encore là. La nappe a un pli, tout près de la miette. Le bois de la caisse est lisse. Une mouche se pose sur la nappe. Elle s'en va. La miette reste. Le parquet est tiède sous le carré. Tu as vu le carré de soleil, Nino ? Oui, papa. Il est chaud. En ce moment, papa pose un cube au sol. Les cubes sentent le bois sec. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Nino attend, un cube orange dans la main. Puis il pose le cube. Le bois fait clic sur le parquet. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Nino. Une règle. On attend. Puis on pose. Oui. On la rappelle. Tu la suis. Plus tard, au jardin, l'air sent l'herbe. Un ballon souple attend près du bac. L'herbe est un peu mouillée sous les pieds. Une règle. On passe le ballon. Puis on s'arrête. On attend. Je me souviens. Comme les cubes. Oui. Je te la rappelle une fois. Nino attend. Puis il passe le ballon. Il s'arrête. L'herbe colle un peu. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. Cubes, puis ballon. Oui. On la rappelle. On la suit. Tu as fait du bon travail. Le bac reste près de l'herbe. Tu as attendu aux cubes, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Nino. Nino essuie ses mains dans l'herbe. Tu as attendu, chaque fois ? Oui. Cubes, puis ballon. Une règle. Je la rappelle. Tu la suis. Le bac sent un peu le plastique chaud. Une goutte d'herbe reste sur le ballon.</t>
+          <t>Une miette de toast reste sur la nappe. Le soleil du matin entre par la fenêtre. Il fait un carré chaud sur le parquet. Une caisse de cubes attend près du tapis. Un cube orange a roulé sous la chaise. L'odeur du toast est encore là. La nappe a un pli, tout près de la miette. Le bois de la caisse est lisse. Une mouche se pose sur la nappe. Elle s'en va. La miette reste. Le parquet est tiède sous le carré. Tu as vu le carré de soleil, Nino ? Oui, papa. Il est chaud. En ce moment, papa pose un cube au sol. Les cubes sentent le bois sec. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Nino attend, un cube orange dans la main. Puis il pose le cube. Le bois fait clic sur le parquet. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Nino. Une règle. On attend. Puis on pose. Oui. On la rappelle. Tu la suis. Plus tard, au jardin, l'air sent l'herbe. Un ballon souple attend près du bac. L'herbe est un peu mouillée sous les pieds. Une règle. On passe le ballon. Puis on s'arrête. On attend. Je me souviens. Comme les cubes. Oui. Je te la rappelle une fois. Nino attend. Puis il passe le ballon. Il s'arrête. L'herbe colle un peu. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. Cubes, puis ballon. Oui. On la rappelle. On la suit. Le bac reste près de l'herbe. Tu as attendu aux cubes, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Nino. Nino essuie ses mains dans l'herbe. Tu as attendu, chaque fois ? Oui. Cubes, puis ballon. Une règle. Je la rappelle. Tu la suis. Le bac sent un peu le plastique chaud. Une goutte d'herbe reste sur le ballon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Henri est dans le salon avec papa. Des cubes sont au sol. Papa dit &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; règle. La règle : on attend. Puis on pose un cube. Henri tend la main. Papa va rappeler la règle une fois. Il dit : on attend. C'est une règle. Henri attend. Puis il pose un cube. Papa dit : tu as suivi la règle. Plus tard, au jardin, papa dit une règle. La règle : on passe le ballon. Puis on s'arrête. Henri veut le ballon. Papa va rappeler la règle une fois. Il dit : on passe, puis on s'arrête. Henri passe le ballon. Il s'arrête. Même leçon, autre jeu. Une règle. La rappeler. Henri la suit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une miette de toast reste sur la nappe. Le soleil du matin entre par la fenêtre. Il fait un carré chaud sur le parquet. Une caisse de cubes attend près du tapis. Un cube orange a roulé sous la chaise. L'odeur du toast est encore là. La nappe a un pli, tout près de la miette. Le bois de la caisse est lisse. Une mouche se pose sur la nappe. Elle s'en va. La miette reste. Le parquet est tiède sous le carré. Tu as vu le carré de soleil, Nino ? Oui, papa. Il est chaud. En ce moment, papa pose un cube au sol. Les cubes sentent le bois sec. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Nino attend, un cube orange dans la main. Puis il pose le cube. Le bois fait clic sur le parquet. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Nino. Une règle. On attend. Puis on pose. Oui. On la rappelle. Tu la suis. Plus tard, au jardin, l'air sent l'herbe. Un ballon souple attend près du bac. L'herbe est un peu mouillée sous les pieds. Une règle. On passe le ballon. Puis on s'arrête. On attend. Je me souviens. Comme les cubes. Oui. Je te la rappelle une fois. Nino attend. Puis il passe le ballon. Il s'arrête. L'herbe colle un peu. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. Cubes, puis ballon. Oui. On la rappelle. On la suit. Le bac reste près de l'herbe. Tu as attendu aux cubes, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Nino. Nino essuie ses mains dans l'herbe. Tu as attendu, chaque fois ? Oui. Cubes, puis ballon. Une règle. Je la rappelle. Tu la suis. Le bac sent un peu le plastique chaud. Une goutte d'herbe reste sur le ballon.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1368,7 +1368,6 @@
 papa|Au ballon, la même règle. Bravo.
 enfant-m|Une règle. Cubes, puis ballon.
 papa|Oui. On la rappelle. On la suit.
-papa|Tu as fait du bon travail.
 narrateur|Le bac reste près de l'herbe.
 papa|Tu as attendu aux cubes, puis au ballon ?
 enfant-m|Oui. Deux jeux. Une règle.
@@ -1410,7 +1409,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Henri joue. Que suit-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino joue. Que suit-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1594,7 +1593,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Henri a suivi &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; règle. Papa l'a rappelée. Cubes, puis ballon.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a suivi une règle. Papa l'a rappelée. Cubes, puis ballon. Deux jeux. Tu as suivi la règle ? Oui, papa. On attend. Bravo. On la rappelle, et on la suit. Le ballon repose près du bac.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1770,7 +1769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le ballon. Henri donne &lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; main.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range le ballon ? Oui, papa. Papa range le ballon dans le bac. Nino donne la main. On rentre. Le toast est fini. Oui. L'herbe est mouillée. Le carré de soleil a bougé. On range aussi les cubes, plus tard ? Oui. Dans la caisse. L'odeur du toast n'est plus là.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1941,12 +1940,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les chaussures de Nino sont un peu humides. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Nino. L'histoire est finie.</t>
+          <t>Les chaussures de Nino sont un peu humides. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Nino.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les chaussures de Nino sont un peu humides. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Nino.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2084,8 +2083,7 @@
           <t>narrateur|Les chaussures de Nino sont un peu humides.
 enfant-m|J'ai attendu. Deux fois.
 papa|Oui. Tu as suivi la règle.
-papa|Bravo, Nino.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Nino.</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2151,6 +2149,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon puis jardin</t>
+          <t>salon le matin, puis jardin, cubes puis ballon</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Henri, papa</t>
+          <t>Nino, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-06.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les cubes de Nino, puis le jardin</t>
+          <t>La tour et le ballon salé</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon le matin, puis jardin, cubes puis ballon</t>
+          <t>maison au bord de mer, cuisine puis terrasse, matin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nino, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nino suit une règle aux cubes, puis au ballon dans l'herbe. Papa rappelle une fois, chaque fois.</t>
+          <t>Raphaël veut une tour plus haute que la coquille, puis le ballon sur la terrasse. Il pose trop tôt, un cube part sous la table. Ils attendent un peu. La tour tient. Le ballon jaune ne part pas aux dunes.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une miette de toast reste sur la nappe. Le soleil du matin entre par la fenêtre. Il fait un carré chaud sur le parquet. Une caisse de cubes attend près du tapis. Un cube orange a roulé sous la chaise. L'odeur du toast est encore là. La nappe a un pli, tout près de la miette. Le bois de la caisse est lisse. Une mouche se pose sur la nappe. Elle s'en va. La miette reste. Le parquet est tiède sous le carré. Tu as vu le carré de soleil, Nino ? Oui, papa. Il est chaud. En ce moment, papa pose un cube au sol. Les cubes sentent le bois sec. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Nino attend, un cube orange dans la main. Puis il pose le cube. Le bois fait clic sur le parquet. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Nino. Une règle. On attend. Puis on pose. Oui. On la rappelle. Tu la suis. Plus tard, au jardin, l'air sent l'herbe. Un ballon souple attend près du bac. L'herbe est un peu mouillée sous les pieds. Une règle. On passe le ballon. Puis on s'arrête. On attend. Je me souviens. Comme les cubes. Oui. Je te la rappelle une fois. Nino attend. Puis il passe le ballon. Il s'arrête. L'herbe colle un peu. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. Cubes, puis ballon. Oui. On la rappelle. On la suit. Le bac reste près de l'herbe. Tu as attendu aux cubes, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Nino. Nino essuie ses mains dans l'herbe. Tu as attendu, chaque fois ? Oui. Cubes, puis ballon. Une règle. Je la rappelle. Tu la suis. Le bac sent un peu le plastique chaud. Une goutte d'herbe reste sur le ballon.</t>
+          <t>Le sel de la mer entre par la fenêtre. Les carreaux de la cuisine sont froids. Une coquille sèche sur le rebord. Dehors, les dunes font un bruit de sable. Les cubes de bois sont près du seau. Le seau sent encore la plage. Raphaël, tu veux une tour ? Oui, papa. Plus haute que la coquille. Papa pose un cube pâle. Le suivant est encore dans sa main. En ce moment, Raphaël se penche. Celui-là, en haut. J'ai pas encore lâché. Raphaël pose trop vite. La tour penche vers le seau. Elle tombe. Un cube part sous la table. Oh. Elle est cassée. La tour s'est arrêtée. On attend un peu ? Raphaël s'arrête à genoux. Le carreau est froid sous les os. Le sel pique un peu les lèvres. Je cherche le cube ? Oui. Sous la table, tout doux. Raphaël rampe un peu. Il touche le bois, collé de sable. Je l'ai. On recommence, un par un. Papa pose le cube pâle, bien à plat. Tu attends que je sois prêt ? Oui. On attend un peu. Raphaël tient le cube, sans le poser. La coquille ne bouge pas sur le rebord. Les dunes chantent encore, plus loin. Une mouette crie, tout haut.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une miette de toast reste sur la nappe. Le soleil du matin entre par la fenêtre. Il fait un carré chaud sur le parquet. Une caisse de cubes attend près du tapis. Un cube orange a roulé sous la chaise. L'odeur du toast est encore là. La nappe a un pli, tout près de la miette. Le bois de la caisse est lisse. Une mouche se pose sur la nappe. Elle s'en va. La miette reste. Le parquet est tiède sous le carré. Tu as vu le carré de soleil, Nino ? Oui, papa. Il est chaud. En ce moment, papa pose un cube au sol. Les cubes sentent le bois sec. Une règle. On attend. Puis on pose un cube. J'ai envie de poser. On attend. Je te la rappelle une fois. C'est la règle. Nino attend, un cube orange dans la main. Puis il pose le cube. Le bois fait clic sur le parquet. Clic. Tu as suivi la règle. Tu as attendu. Bravo, Nino. Une règle. On attend. Puis on pose. Oui. On la rappelle. Tu la suis. Plus tard, au jardin, l'air sent l'herbe. Un ballon souple attend près du bac. L'herbe est un peu mouillée sous les pieds. Une règle. On passe le ballon. Puis on s'arrête. On attend. Je me souviens. Comme les cubes. Oui. Je te la rappelle une fois. Nino attend. Puis il passe le ballon. Il s'arrête. L'herbe colle un peu. Tu as suivi la règle dite. Au ballon, la même règle. Bravo. Une règle. Cubes, puis ballon. Oui. On la rappelle. On la suit. Le bac reste près de l'herbe. Tu as attendu aux cubes, puis au ballon ? Oui. Deux jeux. Une règle. Bravo, Nino. Nino essuie ses mains dans l'herbe. Tu as attendu, chaque fois ? Oui. Cubes, puis ballon. Une règle. Je la rappelle. Tu la suis. Le bac sent un peu le plastique chaud. Une goutte d'herbe reste sur le ballon.</t>
+          <t>Le sel de la mer entre par la fenêtre. Les carreaux de la cuisine sont froids. Une coquille sèche sur le rebord. Dehors, les dunes font un bruit de sable. Les cubes de bois sont près du seau. Le seau sent encore la plage. Raphaël, tu veux une tour ? Oui, papa. Plus haute que la coquille. Papa pose un cube pâle. Le suivant est encore dans sa main. En ce moment, Raphaël se penche. Celui-là, en haut. J'ai pas encore lâché. Raphaël pose trop vite. La tour penche vers le seau. Elle tombe. Un cube part sous la table. Oh. Elle est cassée. La tour s'est arrêtée. On attend un peu ? Raphaël s'arrête à genoux. Le carreau est froid sous les os. Le sel pique un peu les lèvres. Je cherche le cube ? Oui. Sous la table, tout doux. Raphaël rampe un peu. Il touche le bois, collé de sable. Je l'ai. On recommence, un par un. Papa pose le cube pâle, bien à plat. Tu attends que je sois prêt ? Oui. On attend un peu. Raphaël tient le cube, sans le poser. La coquille ne bouge pas sur le rebord. Les dunes chantent encore, plus loin. Une mouette crie, tout haut.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,60 +1324,46 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une miette de toast reste sur la nappe.
-narrateur|Le soleil du matin entre par la fenêtre.
-narrateur|Il fait un carré chaud sur le parquet.
-narrateur|Une caisse de cubes attend près du tapis.
-narrateur|Un cube orange a roulé sous la chaise.
-narrateur|L'odeur du toast est encore là.
-narrateur|La nappe a un pli, tout près de la miette.
-narrateur|Le bois de la caisse est lisse.
-narrateur|Une mouche se pose sur la nappe.
-narrateur|Elle s'en va.
-narrateur|La miette reste.
-narrateur|Le parquet est tiède sous le carré.
-papa|Tu as vu le carré de soleil, Nino ?
-enfant-m|Oui, papa. Il est chaud.
-narrateur|En ce moment, papa pose un cube au sol.
-narrateur|Les cubes sentent le bois sec.
-papa|Une règle. On attend.
-papa|Puis on pose un cube.
-enfant-m|J'ai envie de poser.
-papa|On attend. Je te la rappelle une fois.
-papa|C'est la règle.
-narrateur|Nino attend, un cube orange dans la main.
-narrateur|Puis il pose le cube.
-narrateur|Le bois fait clic sur le parquet.
-enfant-m|Clic.
-papa|Tu as suivi la règle.
-papa|Tu as attendu. Bravo, Nino.
-enfant-m|Une règle. On attend. Puis on pose.
-papa|Oui. On la rappelle. Tu la suis.
-narrateur|Plus tard, au jardin, l'air sent l'herbe.
-narrateur|Un ballon souple attend près du bac.
-narrateur|L'herbe est un peu mouillée sous les pieds.
-papa|Une règle. On passe le ballon.
-papa|Puis on s'arrête. On attend.
-enfant-m|Je me souviens. Comme les cubes.
-papa|Oui. Je te la rappelle une fois.
-narrateur|Nino attend.
-narrateur|Puis il passe le ballon.
-narrateur|Il s'arrête.
-narrateur|L'herbe colle un peu.
-papa|Tu as suivi la règle dite.
-papa|Au ballon, la même règle. Bravo.
-enfant-m|Une règle. Cubes, puis ballon.
-papa|Oui. On la rappelle. On la suit.
-narrateur|Le bac reste près de l'herbe.
-papa|Tu as attendu aux cubes, puis au ballon ?
-enfant-m|Oui. Deux jeux. Une règle.
-papa|Bravo, Nino.
-narrateur|Nino essuie ses mains dans l'herbe.
-papa|Tu as attendu, chaque fois ?
-enfant-m|Oui. Cubes, puis ballon.
-papa|Une règle. Je la rappelle. Tu la suis.
-narrateur|Le bac sent un peu le plastique chaud.
-narrateur|Une goutte d'herbe reste sur le ballon.</t>
+          <t>narrateur|Le sel de la mer entre par la fenêtre.
+narrateur|Les carreaux de la cuisine sont froids.
+narrateur|Une coquille sèche sur le rebord.
+narrateur|Dehors, les dunes font un bruit de sable.
+narrateur|Les cubes de bois sont près du seau.
+narrateur|Le seau sent encore la plage.
+papa|Raphaël, tu veux une tour ?
+enfant-m|Oui, papa.
+enfant-m|Plus haute que la coquille.
+narrateur|Papa pose un cube pâle.
+narrateur|Le suivant est encore dans sa main.
+narrateur|En ce moment, Raphaël se penche.
+enfant-m|Celui-là, en haut.
+papa|J'ai pas encore lâché.
+narrateur|Raphaël pose trop vite.
+narrateur|La tour penche vers le seau.
+narrateur|Elle tombe.
+narrateur|Un cube part sous la table.
+enfant-m|Oh.
+enfant-m|Elle est cassée.
+papa|La tour s'est arrêtée.
+papa|On attend un peu ?
+narrateur|Raphaël s'arrête à genoux.
+narrateur|Le carreau est froid sous les os.
+narrateur|Le sel pique un peu les lèvres.
+enfant-m|Je cherche le cube ?
+papa|Oui.
+papa|Sous la table, tout doux.
+narrateur|Raphaël rampe un peu.
+narrateur|Il touche le bois, collé de sable.
+enfant-m|Je l'ai.
+papa|On recommence, un par un.
+narrateur|Papa pose le cube pâle, bien à plat.
+papa|Tu attends que je sois prêt ?
+enfant-m|Oui.
+papa|On attend un peu.
+narrateur|Raphaël tient le cube, sans le poser.
+narrateur|La coquille ne bouge pas sur le rebord.
+narrateur|Les dunes chantent encore, plus loin.
+narrateur|Une mouette crie, tout haut.</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1390,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nino joue. Que suit-il ?</t>
+          <t>Raphaël veut la tour. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nino joue. Que suit-il ?</t>
+          <t>Raphaël veut la tour. Que fait-il d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1419,12 +1405,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>la règle</t>
+          <t>attendre</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la règle | une règle | attendre | passer</t>
+          <t>attendre | on attend | un peu | son tour | elle attend | il attend | attendre un peu | on attend un peu | à son tour</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1439,7 +1425,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Papa rappelle. Quelle chose Henri suit ?</t>
+          <t>Il reste un peu. Que fait Raphaël d'abord ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1481,14 +1467,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1560,8 +1546,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nino joue.
-narrateur|Que suit-il ?</t>
+          <t>narrateur|Raphaël veut la tour.
+narrateur|Que fait-il d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a suivi une règle. Papa l'a rappelée. Cubes, puis ballon. Deux jeux. Tu as suivi la règle ? Oui, papa. On attend. Bravo. On la rappelle, et on la suit. Le ballon repose près du bac.</t>
+          <t>Raphaël reste encore un peu. Le bas est à plat. Tu peux poser. J'y vais. Il pose tout doux. La tour ne penche pas. Plus haute que la coquille. Oui. Un cube, puis l'autre. Le bois sent le sel, un peu. La tour tient près du seau. Plus tard, le ballon dehors ? Le ballon de la terrasse. On attend un peu, d'abord. Ils regardent encore la tour. Elle ne tombe pas. Merci, Raphaël. Elle est droite. Une mouette passe devant la fenêtre. Son ombre traverse les cubes. On sort les pieds nus ? Oui. Le sable est chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nino a suivi une règle. Papa l'a rappelée. Cubes, puis ballon. Deux jeux. Tu as suivi la règle ? Oui, papa. On attend. Bravo. On la rappelle, et on la suit. Le ballon repose près du bac.</t>
+          <t>Raphaël reste encore un peu. Le bas est à plat. Tu peux poser. J'y vais. Il pose tout doux. La tour ne penche pas. Plus haute que la coquille. Oui. Un cube, puis l'autre. Le bois sent le sel, un peu. La tour tient près du seau. Plus tard, le ballon dehors ? Le ballon de la terrasse. On attend un peu, d'abord. Ils regardent encore la tour. Elle ne tombe pas. Merci, Raphaël. Elle est droite. Une mouette passe devant la fenêtre. Son ombre traverse les cubes. On sort les pieds nus ? Oui. Le sable est chaud.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1656,7 +1642,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1732,12 +1718,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino a suivi une règle.
-narrateur|Papa l'a rappelée. Cubes, puis ballon.
-papa|Deux jeux. Tu as suivi la règle ?
-enfant-m|Oui, papa. On attend.
-papa|Bravo. On la rappelle, et on la suit.
-narrateur|Le ballon repose près du bac.</t>
+          <t>narrateur|Raphaël reste encore un peu.
+papa|Le bas est à plat.
+papa|Tu peux poser.
+enfant-m|J'y vais.
+narrateur|Il pose tout doux.
+narrateur|La tour ne penche pas.
+enfant-m|Plus haute que la coquille.
+papa|Oui.
+papa|Un cube, puis l'autre.
+narrateur|Le bois sent le sel, un peu.
+narrateur|La tour tient près du seau.
+papa|Plus tard, le ballon dehors ?
+enfant-m|Le ballon de la terrasse.
+papa|On attend un peu, d'abord.
+narrateur|Ils regardent encore la tour.
+narrateur|Elle ne tombe pas.
+papa|Merci, Raphaël.
+enfant-m|Elle est droite.
+narrateur|Une mouette passe devant la fenêtre.
+narrateur|Son ombre traverse les cubes.
+papa|On sort les pieds nus ?
+enfant-m|Oui.
+enfant-m|Le sable est chaud.</t>
         </is>
       </c>
     </row>
@@ -1764,12 +1767,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On range le ballon ? Oui, papa. Papa range le ballon dans le bac. Nino donne la main. On rentre. Le toast est fini. Oui. L'herbe est mouillée. Le carré de soleil a bougé. On range aussi les cubes, plus tard ? Oui. Dans la caisse. L'odeur du toast n'est plus là.</t>
+          <t>La terrasse donne sur les dunes. Le bois des lames est chaud, un peu rêche. Le ballon jaune attend près du bac. Je le prends. Attends un peu. Raphaël s'arrête. Le vent pousse déjà le ballon. Si on lance trop tôt, il va au sable. Comme le cube, sous la table. Oui. Mes mains sont ouvertes. Tu es prêt ? Oui, papa. Il envoie le ballon, tout doux. Le ballon ne part pas vers les dunes. Il revient dans les mains de papa. Tu l'as ! Oui. Comme la tour. La mer fait un bruit rond, tout près. Le sel colle encore aux cheveux. On relance ? Oui. Quand j'ai les mains.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On range le ballon ? Oui, papa. Papa range le ballon dans le bac. Nino donne la main. On rentre. Le toast est fini. Oui. L'herbe est mouillée. Le carré de soleil a bougé. On range aussi les cubes, plus tard ? Oui. Dans la caisse. L'odeur du toast n'est plus là.</t>
+          <t>La terrasse donne sur les dunes. Le bois des lames est chaud, un peu rêche. Le ballon jaune attend près du bac. Je le prends. Attends un peu. Raphaël s'arrête. Le vent pousse déjà le ballon. Si on lance trop tôt, il va au sable. Comme le cube, sous la table. Oui. Mes mains sont ouvertes. Tu es prêt ? Oui, papa. Il envoie le ballon, tout doux. Le ballon ne part pas vers les dunes. Il revient dans les mains de papa. Tu l'as ! Oui. Comme la tour. La mer fait un bruit rond, tout près. Le sel colle encore aux cheveux. On relance ? Oui. Quand j'ai les mains.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1832,7 +1835,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1904,16 +1907,30 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>papa|On range le ballon ?
+          <t>narrateur|La terrasse donne sur les dunes.
+narrateur|Le bois des lames est chaud, un peu rêche.
+narrateur|Le ballon jaune attend près du bac.
+enfant-m|Je le prends.
+papa|Attends un peu.
+narrateur|Raphaël s'arrête.
+narrateur|Le vent pousse déjà le ballon.
+papa|Si on lance trop tôt, il va au sable.
+enfant-m|Comme le cube, sous la table.
+papa|Oui.
+papa|Mes mains sont ouvertes.
+papa|Tu es prêt ?
 enfant-m|Oui, papa.
-narrateur|Papa range le ballon dans le bac.
-narrateur|Nino donne la main.
-papa|On rentre. Le toast est fini.
-enfant-m|Oui. L'herbe est mouillée.
-narrateur|Le carré de soleil a bougé.
-papa|On range aussi les cubes, plus tard ?
-enfant-m|Oui. Dans la caisse.
-narrateur|L'odeur du toast n'est plus là.</t>
+narrateur|Il envoie le ballon, tout doux.
+narrateur|Le ballon ne part pas vers les dunes.
+narrateur|Il revient dans les mains de papa.
+enfant-m|Tu l'as !
+papa|Oui.
+papa|Comme la tour.
+narrateur|La mer fait un bruit rond, tout près.
+narrateur|Le sel colle encore aux cheveux.
+enfant-m|On relance ?
+papa|Oui.
+papa|Quand j'ai les mains.</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Les chaussures de Nino sont un peu humides. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Nino.</t>
+          <t>Le ballon est jaune comme le sable. Et toi, tu as attendu. Bravo, Raphaël. La mer chante encore, tout bas. La tour tient derrière la fenêtre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Les chaussures de Nino sont un peu humides. J'ai attendu. Deux fois. Oui. Tu as suivi la règle. Bravo, Nino.</t>
+          <t>Le ballon est jaune comme le sable. Et toi, tu as attendu. Bravo, Raphaël. La mer chante encore, tout bas. La tour tient derrière la fenêtre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2008,7 +2025,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2080,10 +2097,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Les chaussures de Nino sont un peu humides.
-enfant-m|J'ai attendu. Deux fois.
-papa|Oui. Tu as suivi la règle.
-papa|Bravo, Nino.</t>
+          <t>enfant-m|Le ballon est jaune comme le sable.
+papa|Et toi, tu as attendu.
+papa|Bravo, Raphaël.
+narrateur|La mer chante encore, tout bas.
+narrateur|La tour tient derrière la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2154,6 +2172,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
